--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6401" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6402" uniqueCount="961">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2649,10 +2649,14 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: Additional information for the dispenser (new)</t>
+  </si>
+  <si>
+    <t>R5: `MedicationRequest.dispenseRequest.dispenserInstruction` (new:Annotation)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.dispenseRequest.dispenserInstruction` has a context of MedicationRequest.dispenseRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.dispenseRequest.dispenserInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:dispenserInstructionR5.id</t>
@@ -2683,6 +2687,9 @@
   </si>
   <si>
     <t>instructions au dispensateur</t>
+  </si>
+  <si>
+    <t>Provides additional information to the dispenser, for example, counselling to be provided to the patient.</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -20296,7 +20303,9 @@
       <c r="M146" t="s" s="2">
         <v>849</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>850</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>81</v>
@@ -20366,7 +20375,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20377,10 +20386,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20492,10 +20501,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20607,10 +20616,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20650,7 +20659,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>81</v>
@@ -20724,10 +20733,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20753,10 +20762,10 @@
         <v>423</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>175</v>
+        <v>861</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20839,10 +20848,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20958,10 +20967,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20987,13 +20996,13 @@
         <v>838</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21043,7 +21052,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21064,7 +21073,7 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>81</v>
@@ -21075,10 +21084,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21190,10 +21199,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21307,10 +21316,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21426,10 +21435,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21455,10 +21464,10 @@
         <v>770</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21509,7 +21518,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21530,7 +21539,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -21541,10 +21550,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21567,13 +21576,13 @@
         <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21624,7 +21633,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21645,7 +21654,7 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
@@ -21656,10 +21665,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21682,13 +21691,13 @@
         <v>81</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21739,7 +21748,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21760,7 +21769,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21771,10 +21780,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21800,16 +21809,16 @@
         <v>591</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>81</v>
@@ -21858,7 +21867,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21876,10 +21885,10 @@
         <v>81</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -21890,10 +21899,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21919,13 +21928,13 @@
         <v>687</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21975,7 +21984,7 @@
         <v>81</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21993,24 +22002,24 @@
         <v>81</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22036,10 +22045,10 @@
         <v>770</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22090,7 +22099,7 @@
         <v>81</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22108,24 +22117,24 @@
         <v>81</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22148,16 +22157,16 @@
         <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22207,7 +22216,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22225,10 +22234,10 @@
         <v>81</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
@@ -22239,10 +22248,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22265,13 +22274,13 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22322,7 +22331,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22343,7 +22352,7 @@
         <v>81</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>356</v>
@@ -22354,10 +22363,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22383,10 +22392,10 @@
         <v>838</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22437,7 +22446,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22455,10 +22464,10 @@
         <v>81</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -22469,10 +22478,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22584,10 +22593,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22701,10 +22710,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22820,10 +22829,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22849,13 +22858,13 @@
         <v>701</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22884,10 +22893,10 @@
         <v>243</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>81</v>
@@ -22903,7 +22912,7 @@
         <v>139</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>90</v>
@@ -22921,27 +22930,27 @@
         <v>81</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>81</v>
@@ -22966,13 +22975,13 @@
         <v>187</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23002,7 +23011,7 @@
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -23020,7 +23029,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>90</v>
@@ -23038,24 +23047,24 @@
         <v>81</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23081,10 +23090,10 @@
         <v>187</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23114,10 +23123,10 @@
         <v>243</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -23135,7 +23144,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23153,24 +23162,24 @@
         <v>81</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23193,13 +23202,13 @@
         <v>81</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23250,7 +23259,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23265,13 +23274,13 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>81</v>
@@ -23282,14 +23291,14 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -23308,16 +23317,16 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23367,7 +23376,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23388,7 +23397,7 @@
         <v>81</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -23399,10 +23408,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23425,16 +23434,16 @@
         <v>81</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23484,7 +23493,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23499,13 +23508,13 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
